--- a/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
+++ b/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
@@ -6320,26 +6320,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6538,26 +6538,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6659,26 +6659,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6780,26 +6780,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6901,26 +6901,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7022,26 +7022,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36782,7 +36782,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>33</v>
@@ -40642,7 +40642,7 @@
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">PL!D70/itc_26</f>
-        <v>0.00556878192679601</v>
+        <v>0.00556878192679602</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">PL!E70/itc_27</f>

--- a/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
+++ b/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
@@ -36874,7 +36874,7 @@
         <v>65</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.421833385510356</v>
+        <v>0.445687059095763</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>33</v>
@@ -36897,7 +36897,7 @@
         <v>65</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.400741716234838</v>
+        <v>0.423402706140975</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>33</v>
@@ -36920,7 +36920,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.37965004695932</v>
+        <v>0.401118353186187</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>33</v>
@@ -36943,7 +36943,7 @@
         <v>65</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.358558377683802</v>
+        <v>0.378834000231398</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>33</v>
@@ -40537,19 +40537,19 @@
       </c>
       <c r="C7" s="16" t="n">
         <f aca="false">inl_26</f>
-        <v>0.421833385510356</v>
+        <v>0.445687059095763</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">inl_27</f>
-        <v>0.400741716234838</v>
+        <v>0.423402706140975</v>
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">inl_28</f>
-        <v>0.37965004695932</v>
+        <v>0.401118353186187</v>
       </c>
       <c r="F7" s="16" t="n">
         <f aca="false">inl_29</f>
-        <v>0.358558377683802</v>
+        <v>0.378834000231398</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>508</v>
@@ -40564,19 +40564,19 @@
       </c>
       <c r="C8" s="16" t="n">
         <f aca="false">C6+C7</f>
-        <v>0.568172962239275</v>
+        <v>0.592026635824682</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">D6+D7</f>
-        <v>0.561715250636648</v>
+        <v>0.584376240542786</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">E6+E7</f>
-        <v>0.547940560197576</v>
+        <v>0.569408866424443</v>
       </c>
       <c r="F8" s="16" t="n">
         <f aca="false">F6+F7</f>
-        <v>0.526848890922058</v>
+        <v>0.547124513469654</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>510</v>
@@ -40615,19 +40615,19 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">C4+C5-C7*C4-C9</f>
-        <v>13.1488009931788</v>
+        <v>12.4390763933297</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">D4+D5-D7*D4-D9</f>
-        <v>26.0119310494969</v>
+        <v>24.7981922275164</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">E4+E5-E7*E4-E9</f>
-        <v>31.6925800033023</v>
+        <v>30.4476007227469</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">F4+F5-F7*F4-F9</f>
-        <v>43.9070695103779</v>
+        <v>42.4282710349935</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>513</v>
@@ -46553,15 +46553,15 @@
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.568172962239275</v>
+        <v>0.592026635824682</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.568172962239275</v>
+        <v>0.592026635824682</v>
       </c>
       <c r="G15" s="16" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.568172962239275</v>
+        <v>0.592026635824682</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>768</v>
@@ -46576,15 +46576,15 @@
       </c>
       <c r="C16" s="16" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.547940560197576</v>
+        <v>0.569408866424443</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.547940560197576</v>
+        <v>0.569408866424443</v>
       </c>
       <c r="G16" s="16" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.547940560197576</v>
+        <v>0.569408866424443</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>771</v>

--- a/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
+++ b/cohr/dist/20261026_Coherent模型_v0.2.2.xlsx
@@ -6026,26 +6026,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中際旭創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">innolight/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中際旭創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
